--- a/data/trans_dic/P62A$invalidez-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 14,46</t>
+          <t>5,63; 14,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 21,89</t>
+          <t>10,02; 20,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,88</t>
+          <t>4,25; 13,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,45</t>
+          <t>0,94; 5,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 14,36</t>
+          <t>4,51; 14,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 13,48</t>
+          <t>4,28; 13,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 14,83</t>
+          <t>4,57; 15,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,07; 50,42</t>
+          <t>40,47; 50,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 12,29</t>
+          <t>6,01; 12,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 16,39</t>
+          <t>8,98; 16,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,14</t>
+          <t>5,48; 11,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,3; 26,5</t>
+          <t>20,52; 26,42</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,52</t>
+          <t>6,11; 13,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,1; 22,88</t>
+          <t>12,97; 23,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 16,26</t>
+          <t>8,03; 16,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 15,22</t>
+          <t>5,61; 15,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 16,07</t>
+          <t>6,83; 16,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,08</t>
+          <t>4,12; 11,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,62; 49,09</t>
+          <t>39,35; 49,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,94</t>
+          <t>6,88; 12,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,4; 18,34</t>
+          <t>11,27; 18,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,56</t>
+          <t>7,15; 12,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,59; 24,61</t>
+          <t>18,41; 24,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 19,4</t>
+          <t>8,01; 18,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,64; 27,24</t>
+          <t>14,01; 27,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,88</t>
+          <t>4,0; 13,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,04</t>
+          <t>0,66; 4,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 14,37</t>
+          <t>3,65; 14,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 19,29</t>
+          <t>6,82; 20,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 14,72</t>
+          <t>4,56; 14,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 36,32</t>
+          <t>3,97; 36,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 14,43</t>
+          <t>7,32; 14,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,09; 20,66</t>
+          <t>12,5; 21,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,72</t>
+          <t>5,32; 12,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 17,07</t>
+          <t>3,84; 16,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 13,7</t>
+          <t>5,09; 13,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,12</t>
+          <t>9,72; 19,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 15,08</t>
+          <t>6,82; 15,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,32; 2,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 11,5</t>
+          <t>3,97; 11,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,5</t>
+          <t>7,36; 16,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,83</t>
+          <t>3,62; 10,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,69; 38,44</t>
+          <t>29,67; 38,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,3</t>
+          <t>5,51; 11,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 16,52</t>
+          <t>9,4; 16,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 11,11</t>
+          <t>5,92; 10,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,37; 20,64</t>
+          <t>15,13; 20,68</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,21</t>
+          <t>7,73; 12,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,9; 19,28</t>
+          <t>13,69; 19,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,78; 12,11</t>
+          <t>7,95; 11,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,26</t>
+          <t>0,81; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,58</t>
+          <t>6,11; 10,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 13,12</t>
+          <t>8,26; 13,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,26</t>
+          <t>5,48; 9,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,15; 40,27</t>
+          <t>16,01; 40,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,81</t>
+          <t>7,66; 10,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,9; 15,59</t>
+          <t>12,03; 15,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,31</t>
+          <t>7,28; 10,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,43; 20,05</t>
+          <t>11,42; 20,11</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de invalidez</t>
+          <t>Población que, al menos, percibe una pensión de invalidez (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9663; 24746</t>
+          <t>9629; 24882</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22511; 46296</t>
+          <t>21185; 44217</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8746; 24414</t>
+          <t>8062; 24763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1606; 9805</t>
+          <t>1684; 9415</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5666; 18182</t>
+          <t>5708; 18021</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7441; 22103</t>
+          <t>7025; 22528</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7120; 22111</t>
+          <t>6820; 22515</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68156; 85750</t>
+          <t>68830; 85769</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17270; 36582</t>
+          <t>17907; 36765</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33068; 61531</t>
+          <t>33724; 61082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18836; 41091</t>
+          <t>18556; 39713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71069; 92750</t>
+          <t>71821; 92494</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13202; 30081</t>
+          <t>13586; 30717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32256; 56332</t>
+          <t>31939; 57245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21930; 43019</t>
+          <t>21251; 44590</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1321</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7766; 23339</t>
+          <t>8605; 23323</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14307; 33716</t>
+          <t>14335; 33948</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8110; 22591</t>
+          <t>8405; 23694</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71245; 90547</t>
+          <t>72593; 91434</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25253; 48641</t>
+          <t>25851; 48064</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51988; 83618</t>
+          <t>51375; 82220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32938; 58841</t>
+          <t>33507; 60521</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71122; 94154</t>
+          <t>70428; 94090</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12735; 29946</t>
+          <t>12372; 28869</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23016; 45973</t>
+          <t>23648; 46495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8189; 23452</t>
+          <t>7285; 24130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1437; 10125</t>
+          <t>1327; 9013</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4354; 17220</t>
+          <t>4375; 17159</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9834; 28520</t>
+          <t>10082; 29775</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5536; 19943</t>
+          <t>6182; 20153</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11998; 126220</t>
+          <t>13788; 127507</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19530; 39553</t>
+          <t>20077; 40389</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38273; 65414</t>
+          <t>39572; 69423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15654; 37217</t>
+          <t>16898; 39051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21250; 93623</t>
+          <t>21070; 91065</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8986; 26006</t>
+          <t>9666; 26091</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23186; 46776</t>
+          <t>23788; 48490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18202; 39972</t>
+          <t>18086; 39853</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 7485</t>
+          <t>710; 6628</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6976; 20263</t>
+          <t>6994; 21060</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16103; 34784</t>
+          <t>16520; 36263</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8112; 24434</t>
+          <t>9004; 26086</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69928; 90543</t>
+          <t>69888; 90837</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20244; 41361</t>
+          <t>20172; 40910</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45303; 77481</t>
+          <t>44110; 75606</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30396; 57076</t>
+          <t>30432; 55471</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70370; 94520</t>
+          <t>69296; 94726</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56950; 90081</t>
+          <t>57073; 90981</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>121069; 167919</t>
+          <t>119227; 166327</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70139; 109097</t>
+          <t>71692; 106875</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5744; 18124</t>
+          <t>6516; 18862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34552; 60976</t>
+          <t>35221; 63012</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>62587; 97897</t>
+          <t>61610; 97220</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39438; 68248</t>
+          <t>40367; 72055</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>142082; 377571</t>
+          <t>150140; 379394</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>101582; 142040</t>
+          <t>100677; 140889</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192494; 252181</t>
+          <t>194534; 252031</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119920; 168861</t>
+          <t>119274; 166609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>198735; 348746</t>
+          <t>198670; 349740</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$invalidez-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62A$invalidez-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 14,54</t>
+          <t>5,75; 14,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 20,91</t>
+          <t>10,25; 20,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 13,07</t>
+          <t>4,42; 12,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,23</t>
+          <t>0,8; 4,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 14,23</t>
+          <t>4,52; 14,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,73</t>
+          <t>4,53; 13,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 15,1</t>
+          <t>4,63; 14,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,47; 50,43</t>
+          <t>40,14; 50,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,01; 12,35</t>
+          <t>5,98; 12,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 16,27</t>
+          <t>9,16; 16,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,73</t>
+          <t>5,53; 11,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,52; 26,42</t>
+          <t>19,66; 26,18</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 13,8</t>
+          <t>5,85; 14,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,97; 23,25</t>
+          <t>12,79; 22,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 16,85</t>
+          <t>8,24; 16,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 15,21</t>
+          <t>5,95; 15,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 16,19</t>
+          <t>6,93; 15,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 11,62</t>
+          <t>4,14; 11,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,35; 49,57</t>
+          <t>38,58; 48,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 12,79</t>
+          <t>6,82; 13,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,27; 18,03</t>
+          <t>11,37; 18,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 12,92</t>
+          <t>7,06; 12,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 24,59</t>
+          <t>17,9; 24,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 18,7</t>
+          <t>7,76; 18,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,01; 27,55</t>
+          <t>13,87; 27,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 13,25</t>
+          <t>4,07; 13,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,49</t>
+          <t>0,79; 5,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 14,32</t>
+          <t>3,33; 14,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 20,14</t>
+          <t>7,11; 20,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,88</t>
+          <t>4,15; 14,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 36,69</t>
+          <t>27,77; 40,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 14,73</t>
+          <t>6,96; 14,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,5; 21,93</t>
+          <t>12,35; 21,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,3</t>
+          <t>5,28; 11,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 16,61</t>
+          <t>12,35; 18,63</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 13,74</t>
+          <t>4,67; 13,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,72; 19,82</t>
+          <t>9,39; 19,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 15,04</t>
+          <t>6,91; 15,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,98</t>
+          <t>0,31; 3,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 11,95</t>
+          <t>4,35; 11,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 16,16</t>
+          <t>7,47; 16,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 10,49</t>
+          <t>3,18; 9,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,67; 38,57</t>
+          <t>28,88; 37,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,17</t>
+          <t>5,4; 11,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 16,12</t>
+          <t>9,42; 16,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,8</t>
+          <t>5,88; 11,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,13; 20,68</t>
+          <t>15,72; 21,2</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,33</t>
+          <t>7,89; 12,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 19,09</t>
+          <t>13,92; 19,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,86</t>
+          <t>7,98; 11,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,35</t>
+          <t>0,73; 2,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,94</t>
+          <t>6,18; 10,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,03</t>
+          <t>8,36; 13,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,78</t>
+          <t>5,51; 9,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,01; 40,46</t>
+          <t>36,25; 41,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,72</t>
+          <t>7,56; 10,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,03; 15,58</t>
+          <t>11,99; 15,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 10,17</t>
+          <t>7,21; 10,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,42; 20,11</t>
+          <t>17,84; 20,89</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77421</t>
+          <t>81496</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81791</t>
+          <t>85942</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9629; 24882</t>
+          <t>9836; 25473</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21185; 44217</t>
+          <t>21674; 43815</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8062; 24763</t>
+          <t>8383; 23810</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1684; 9415</t>
+          <t>1577; 9231</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5708; 18021</t>
+          <t>5725; 18420</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7025; 22528</t>
+          <t>7426; 22763</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6820; 22515</t>
+          <t>6903; 22075</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68830; 85769</t>
+          <t>72769; 91639</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17907; 36765</t>
+          <t>17802; 37028</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33724; 61082</t>
+          <t>34387; 61714</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18556; 39713</t>
+          <t>18733; 39712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71821; 92494</t>
+          <t>74314; 98953</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>88633</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81603</t>
+          <t>88633</t>
         </is>
       </c>
     </row>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13586; 30717</t>
+          <t>13028; 31716</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31939; 57245</t>
+          <t>31489; 56319</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21251; 44590</t>
+          <t>21801; 43490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1873,42 +1873,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8605; 23323</t>
+          <t>9128; 24140</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14335; 33948</t>
+          <t>14541; 33038</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8405; 23694</t>
+          <t>8444; 22698</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72593; 91434</t>
+          <t>78498; 98672</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25851; 48064</t>
+          <t>25636; 48965</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51375; 82220</t>
+          <t>51853; 82535</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33507; 60521</t>
+          <t>33091; 59624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70428; 94090</t>
+          <t>75712; 101927</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49577</t>
+          <t>55167</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53716</t>
+          <t>59597</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12372; 28869</t>
+          <t>11983; 28731</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23648; 46495</t>
+          <t>23409; 45887</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7285; 24130</t>
+          <t>7411; 24326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1327; 9013</t>
+          <t>1782; 11655</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4375; 17159</t>
+          <t>3991; 17063</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10082; 29775</t>
+          <t>10517; 30027</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6182; 20153</t>
+          <t>5619; 19817</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13788; 127507</t>
+          <t>45080; 65214</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20077; 40389</t>
+          <t>19093; 39512</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39572; 69423</t>
+          <t>39089; 67236</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16898; 39051</t>
+          <t>16757; 37990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21070; 91065</t>
+          <t>48029; 72419</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>79747</t>
+          <t>85910</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82386</t>
+          <t>88675</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9666; 26091</t>
+          <t>8866; 25286</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23788; 48490</t>
+          <t>22983; 48561</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18086; 39853</t>
+          <t>18317; 40030</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>710; 6628</t>
+          <t>722; 7443</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6994; 21060</t>
+          <t>7660; 20239</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16520; 36263</t>
+          <t>16755; 36279</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9004; 26086</t>
+          <t>7899; 24759</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69888; 90837</t>
+          <t>74159; 97326</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20172; 40910</t>
+          <t>19783; 41106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44110; 75606</t>
+          <t>44177; 75588</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30432; 55471</t>
+          <t>30199; 57127</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69296; 94726</t>
+          <t>76786; 103597</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>288348</t>
+          <t>311206</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>299495</t>
+          <t>322848</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57073; 90981</t>
+          <t>58227; 90227</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>119227; 166327</t>
+          <t>121248; 166025</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71692; 106875</t>
+          <t>71919; 107131</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6516; 18862</t>
+          <t>6342; 19634</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35221; 63012</t>
+          <t>35608; 60881</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61610; 97220</t>
+          <t>62373; 98199</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40367; 72055</t>
+          <t>40608; 70976</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>150140; 379394</t>
+          <t>291430; 332244</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100677; 140889</t>
+          <t>99271; 142305</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194534; 252031</t>
+          <t>193943; 253555</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119274; 166609</t>
+          <t>118089; 164143</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>198670; 349740</t>
+          <t>299363; 350622</t>
         </is>
       </c>
     </row>
